--- a/Context/Fake_ML.xlsx
+++ b/Context/Fake_ML.xlsx
@@ -766,7 +766,7 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
         <v>0.19</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J16" t="n">
         <v>0.4</v>
@@ -2376,7 +2376,7 @@
         <v>0.055</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2866,7 +2866,7 @@
         <v>0.19</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J35" t="n">
         <v>0.4</v>
@@ -3496,7 +3496,7 @@
         <v>0.23</v>
       </c>
       <c r="I44" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
         <v>0.23</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J69" t="n">
         <v>0.4</v>
@@ -5736,7 +5736,7 @@
         <v>0.19</v>
       </c>
       <c r="I76" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -6296,7 +6296,7 @@
         <v>0.055</v>
       </c>
       <c r="I84" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -6856,7 +6856,7 @@
         <v>0.2</v>
       </c>
       <c r="I92" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J92" t="n">
         <v>0.4</v>
@@ -7416,7 +7416,7 @@
         <v>0.19</v>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -7976,7 +7976,7 @@
         <v>0.2</v>
       </c>
       <c r="I108" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J108" t="n">
         <v>0.4</v>
@@ -8256,7 +8256,7 @@
         <v>0.19</v>
       </c>
       <c r="I112" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -9376,7 +9376,7 @@
         <v>0.19</v>
       </c>
       <c r="I128" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J128" t="n">
         <v>0.4</v>
@@ -9936,7 +9936,7 @@
         <v>0.21</v>
       </c>
       <c r="I136" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -10496,7 +10496,7 @@
         <v>0.23</v>
       </c>
       <c r="I144" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -11616,7 +11616,7 @@
         <v>0.23</v>
       </c>
       <c r="I160" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -12176,7 +12176,7 @@
         <v>0.21</v>
       </c>
       <c r="I168" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -12456,7 +12456,7 @@
         <v>0.23</v>
       </c>
       <c r="I172" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -13016,7 +13016,7 @@
         <v>0.21</v>
       </c>
       <c r="I180" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -13576,7 +13576,7 @@
         <v>0.21</v>
       </c>
       <c r="I188" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J188" t="n">
         <v>0.4</v>
